--- a/HPB_Templates/Technique_TestName_TestResult_TestUnit_export.xlsx
+++ b/HPB_Templates/Technique_TestName_TestResult_TestUnit_export.xlsx
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Decreased</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Decreased</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -7222,7 +7222,11 @@
           <t>U/mL</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
           <t>37</t>
